--- a/public/downloads/sales-invoice-template.xlsx
+++ b/public/downloads/sales-invoice-template.xlsx
@@ -855,7 +855,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="10">
-        <v>46160.56948086806</v>
+        <v>46160.58105515046</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
